--- a/Result/profitability/8089.xlsx
+++ b/Result/profitability/8089.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM52"/>
+  <dimension ref="A1:AM53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3900000000000001</v>
+        <v>-0.3212499999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>34.91125</v>
+        <v>35.74375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04875000000000018</v>
+        <v>-0.1124999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>35.0325</v>
+        <v>36.74875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03750000000000019</v>
+        <v>-0.01249999999999987</v>
       </c>
       <c r="N4" t="n">
-        <v>35.73</v>
+        <v>36.42375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1237500000000002</v>
+        <v>0.2362500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>35.16</v>
+        <v>35.2025</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,16 +1137,16 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3375000000000002</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>33.90625</v>
+        <v>31.53875</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-5.12</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2624999999999998</v>
+        <v>-0.1724999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>28.66</v>
+        <v>29.6225</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7032,6 +7032,133 @@
       </c>
       <c r="AM52" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>8089</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>114</v>
+      </c>
+      <c r="D53" t="n">
+        <v>67</v>
+      </c>
+      <c r="E53" t="n">
+        <v>46</v>
+      </c>
+      <c r="F53" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-50</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-44.04%</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>17</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-33</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-34</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.1700000000000002</v>
+      </c>
+      <c r="N53" t="n">
+        <v>36.6025</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="X53" t="n">
+        <v>-0.4583333333333333</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.808340727595386</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-0.6338028169014085</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.3399999999999963</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.008411677387431871</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
